--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4057" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -509,6 +509,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -698,6 +701,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -708,10 +714,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -724,6 +745,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -731,6 +761,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -738,6 +771,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -1111,6 +1147,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1487,7 +1529,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4526,7 +4568,9 @@
       <c r="K30" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L30" s="2"/>
+      <c r="L30" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4597,10 +4641,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4634,7 +4678,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>74</v>
@@ -4656,7 +4700,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4674,7 +4718,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4694,10 +4738,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4731,7 +4775,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4753,7 +4797,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4771,7 +4815,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4791,10 +4835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4808,7 +4852,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4820,10 +4864,10 @@
         <v>95</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4874,7 +4918,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4894,10 +4938,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4911,7 +4955,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4920,13 +4964,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4977,7 +5021,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4997,10 +5041,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5098,10 +5142,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5130,7 +5174,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5142,7 +5186,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5181,7 +5225,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5201,17 +5245,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
@@ -5233,7 +5277,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5245,7 +5289,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5284,7 +5328,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5304,17 +5348,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5336,7 +5380,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5348,7 +5392,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5387,7 +5431,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5407,17 +5451,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5439,7 +5483,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5490,7 +5534,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5510,17 +5554,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>75</v>
@@ -5542,7 +5586,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5554,7 +5598,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5593,7 +5637,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5613,10 +5657,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5639,11 +5683,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5694,7 +5738,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5714,10 +5758,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5744,7 +5788,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5795,7 +5839,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5815,17 +5859,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5843,11 +5887,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5898,7 +5942,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5918,17 +5962,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5946,11 +5990,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6001,7 +6045,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6021,17 +6065,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6049,11 +6093,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6104,7 +6148,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6124,10 +6168,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6141,7 +6185,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6150,16 +6194,18 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6207,7 +6253,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6227,10 +6273,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6244,7 +6290,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6253,15 +6299,17 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>74</v>
@@ -6310,7 +6358,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6330,10 +6378,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6356,12 +6404,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6409,7 +6461,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6429,10 +6481,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6457,10 +6509,14 @@
       <c r="K49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L49" s="2"/>
+      <c r="L49" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
       </c>
@@ -6488,7 +6544,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6506,7 +6562,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6526,10 +6582,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6552,12 +6608,18 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>74</v>
       </c>
@@ -6605,7 +6667,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6625,10 +6687,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6651,12 +6713,14 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
@@ -6704,7 +6768,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6724,10 +6788,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6750,12 +6814,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6803,7 +6869,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6823,10 +6889,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6840,7 +6906,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6849,7 +6915,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6890,7 +6956,7 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -6900,7 +6966,7 @@
         <v>124</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6920,13 +6986,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -6948,7 +7014,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -7001,7 +7067,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7021,10 +7087,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7122,10 +7188,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7223,10 +7289,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7324,10 +7390,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7425,10 +7491,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7528,10 +7594,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7631,10 +7697,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7734,10 +7800,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7837,10 +7903,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7938,10 +8004,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7971,7 +8037,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
@@ -7997,7 +8063,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -8015,7 +8081,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8035,10 +8101,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8072,7 +8138,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8114,7 +8180,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8134,10 +8200,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8160,7 +8226,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8213,7 +8279,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8233,10 +8299,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8259,7 +8325,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8312,7 +8378,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8332,10 +8398,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8358,7 +8424,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8411,7 +8477,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8431,10 +8497,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8457,7 +8523,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8510,7 +8576,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8530,10 +8596,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8556,7 +8622,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8609,7 +8675,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8629,10 +8695,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8655,10 +8721,10 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -8710,7 +8776,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8730,10 +8796,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8756,7 +8822,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8809,7 +8875,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8829,10 +8895,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8855,7 +8921,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8908,7 +8974,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8928,10 +8994,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8954,7 +9020,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -9007,7 +9073,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9027,13 +9093,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>74</v>
@@ -9055,7 +9121,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9108,7 +9174,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9128,10 +9194,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9229,10 +9295,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9330,10 +9396,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9431,10 +9497,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9532,10 +9598,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9635,10 +9701,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9738,10 +9804,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9841,10 +9907,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9944,10 +10010,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10045,10 +10111,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10078,7 +10144,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
@@ -10104,7 +10170,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10122,7 +10188,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10142,10 +10208,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10179,7 +10245,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>74</v>
@@ -10221,7 +10287,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10241,10 +10307,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10267,7 +10333,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10320,7 +10386,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10340,10 +10406,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10366,7 +10432,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10419,7 +10485,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10439,10 +10505,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10465,10 +10531,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10520,7 +10586,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10540,10 +10606,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10566,7 +10632,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10619,7 +10685,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10639,10 +10705,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10665,7 +10731,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10718,7 +10784,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10738,10 +10804,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10764,7 +10830,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10817,7 +10883,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10837,10 +10903,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10863,7 +10929,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10916,7 +10982,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10936,10 +11002,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10962,7 +11028,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11015,7 +11081,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11035,10 +11101,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11061,7 +11127,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11114,7 +11180,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11134,13 +11200,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>74</v>
@@ -11162,7 +11228,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11215,7 +11281,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11235,10 +11301,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11336,10 +11402,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11437,10 +11503,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11538,10 +11604,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11639,10 +11705,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11742,10 +11808,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11845,10 +11911,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11948,10 +12014,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12051,10 +12117,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12152,10 +12218,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12185,7 +12251,7 @@
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12211,7 +12277,7 @@
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
@@ -12229,7 +12295,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12249,10 +12315,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12286,7 +12352,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>74</v>
@@ -12328,7 +12394,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12348,10 +12414,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12374,10 +12440,10 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -12429,7 +12495,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12449,10 +12515,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12475,7 +12541,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12528,7 +12594,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12548,10 +12614,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12574,7 +12640,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12627,7 +12693,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12647,10 +12713,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12673,7 +12739,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12726,7 +12792,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12746,10 +12812,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12772,7 +12838,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12825,7 +12891,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12845,10 +12911,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12871,7 +12937,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -12924,7 +12990,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -12944,10 +13010,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12970,7 +13036,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13023,7 +13089,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13043,10 +13109,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13069,7 +13135,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13122,7 +13188,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13142,10 +13208,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13168,7 +13234,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13221,7 +13287,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13241,10 +13307,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13267,12 +13333,16 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="L117" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>74</v>
       </c>
@@ -13320,7 +13390,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13340,10 +13410,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13441,10 +13511,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13542,10 +13612,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13643,10 +13713,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13744,10 +13814,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13847,10 +13917,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13950,10 +14020,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14053,10 +14123,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14156,10 +14226,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14257,10 +14327,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14287,7 +14357,7 @@
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14296,7 +14366,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>74</v>
@@ -14338,7 +14408,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14358,10 +14428,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14395,7 +14465,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>74</v>
@@ -14437,7 +14507,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14457,10 +14527,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14483,7 +14553,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14536,7 +14606,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
